--- a/hourly datasets/cap_gen_year-4final.xlsx
+++ b/hourly datasets/cap_gen_year-4final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1162205337124879</v>
+        <v>0.1154935276693017</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1159475776526635</v>
+        <v>0.1151689754377776</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2321681113651514</v>
+        <v>0.2306625031070793</v>
       </c>
     </row>
     <row r="4">
@@ -513,25 +513,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.13357075316607</v>
+        <v>0.1320184843607762</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01179703357937737</v>
+        <v>0.01170019730839802</v>
       </c>
       <c r="D4" t="n">
-        <v>20.58699692357818</v>
+        <v>20.33795207942311</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03033988233797874</v>
+        <v>0.02942285767024194</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1104444260845312</v>
+        <v>0.1090819976461664</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1566970802476083</v>
+        <v>0.154954971075386</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2497912868785579</v>
+        <v>0.247512012030078</v>
       </c>
     </row>
     <row r="5">
@@ -541,25 +541,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1228575463317561</v>
+        <v>0.1229358397398398</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008156771566143299</v>
+        <v>0.008153486261766405</v>
       </c>
       <c r="D5" t="n">
-        <v>20.46737717312538</v>
+        <v>20.49766085983692</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02866258988314367</v>
+        <v>0.02872852238743644</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1068683027896997</v>
+        <v>0.106953036402549</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1388467898738125</v>
+        <v>0.1389186430771301</v>
       </c>
       <c r="H5" t="n">
-        <v>0.239078080044244</v>
+        <v>0.2384293674091415</v>
       </c>
     </row>
     <row r="6">
@@ -569,25 +569,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08791383177406166</v>
+        <v>0.08784781135881332</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00840672631726566</v>
+        <v>0.008400432006278878</v>
       </c>
       <c r="D6" t="n">
-        <v>5.306776804638185</v>
+        <v>5.302672238745703</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004379439210882941</v>
+        <v>0.004269925483494016</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07143459776743939</v>
+        <v>0.07138091588087987</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1043930657806837</v>
+        <v>0.1043147068367472</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2041343654865496</v>
+        <v>0.2033413390281151</v>
       </c>
     </row>
     <row r="7">
@@ -597,25 +597,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1007887833569711</v>
+        <v>0.1007733505490333</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008340925827625694</v>
+        <v>0.008339427380790658</v>
       </c>
       <c r="D7" t="n">
-        <v>5.521294417558253</v>
+        <v>5.518479211794017</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002768320724300602</v>
+        <v>0.0002769676848125113</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08443854454145189</v>
+        <v>0.08442604931908698</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1171390221724903</v>
+        <v>0.1171206517789791</v>
       </c>
       <c r="H7" t="n">
-        <v>0.217009317069459</v>
+        <v>0.216266878218335</v>
       </c>
     </row>
     <row r="8">
@@ -625,25 +625,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08076945253612626</v>
+        <v>0.08075139283429086</v>
       </c>
       <c r="C8" t="n">
-        <v>0.005160975709345611</v>
+        <v>0.005159491644942366</v>
       </c>
       <c r="D8" t="n">
-        <v>5.300585579962204</v>
+        <v>5.299644615466241</v>
       </c>
       <c r="E8" t="n">
-        <v>2.207715863492478e-41</v>
+        <v>2.174010277790305e-41</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07065268261852077</v>
+        <v>0.0706375321450093</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09088622245373243</v>
+        <v>0.09086525352357294</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1969899862486142</v>
+        <v>0.1962449205035926</v>
       </c>
     </row>
     <row r="9">
@@ -653,25 +653,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0839124389506023</v>
+        <v>0.08389329607192834</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004715800976607847</v>
+        <v>0.004714228005401442</v>
       </c>
       <c r="D9" t="n">
-        <v>6.032688380303757</v>
+        <v>6.031779678291385</v>
       </c>
       <c r="E9" t="n">
-        <v>5.06214135483377e-44</v>
+        <v>4.984856753996613e-44</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07466831928774365</v>
+        <v>0.07465225991802206</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09315655861346119</v>
+        <v>0.09313433222583486</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2001329726630902</v>
+        <v>0.1993868237412301</v>
       </c>
     </row>
     <row r="10">
@@ -681,25 +681,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07958893669482638</v>
+        <v>0.07956891151227333</v>
       </c>
       <c r="C10" t="n">
-        <v>0.004286041305547478</v>
+        <v>0.004284433690004747</v>
       </c>
       <c r="D10" t="n">
-        <v>6.300713455353969</v>
+        <v>6.299803315822223</v>
       </c>
       <c r="E10" t="n">
-        <v>1.151425826643004e-45</v>
+        <v>1.133846806388912e-45</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0711872501973065</v>
+        <v>0.07117037643419094</v>
       </c>
       <c r="G10" t="n">
-        <v>0.08799062319234656</v>
+        <v>0.08796744659035587</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1958094704073143</v>
+        <v>0.1950624391815751</v>
       </c>
     </row>
     <row r="11">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03852213677568325</v>
+        <v>0.03818192031798831</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -717,7 +717,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1547426704881712</v>
+        <v>0.15367544798729</v>
       </c>
     </row>
     <row r="12">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05231807266108257</v>
+        <v>0.05112482702232342</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -735,7 +735,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1685386063735705</v>
+        <v>0.1666183546916252</v>
       </c>
     </row>
     <row r="13">
@@ -745,25 +745,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05934863508450505</v>
+        <v>0.05730233015657719</v>
       </c>
       <c r="C13" t="n">
-        <v>0.008941158084238263</v>
+        <v>0.008944364535980229</v>
       </c>
       <c r="D13" t="n">
-        <v>8.20126881744941</v>
+        <v>7.787680738114978</v>
       </c>
       <c r="E13" t="n">
-        <v>0.03927449497572273</v>
+        <v>0.04035651114324693</v>
       </c>
       <c r="F13" t="n">
-        <v>0.04182032212418055</v>
+        <v>0.03976774481781017</v>
       </c>
       <c r="G13" t="n">
-        <v>0.07687694804482947</v>
+        <v>0.07483691549534413</v>
       </c>
       <c r="H13" t="n">
-        <v>0.175569168796993</v>
+        <v>0.1727958578258789</v>
       </c>
     </row>
     <row r="14">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06494635472541754</v>
+        <v>0.06315694696446089</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -781,7 +781,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1811668884379055</v>
+        <v>0.1786504746337626</v>
       </c>
     </row>
     <row r="15">
@@ -791,25 +791,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07194714387278678</v>
+        <v>0.06990403105257292</v>
       </c>
       <c r="C15" t="n">
-        <v>0.008770652708367917</v>
+        <v>0.008753978502926555</v>
       </c>
       <c r="D15" t="n">
-        <v>10.61273806437143</v>
+        <v>10.17803388647727</v>
       </c>
       <c r="E15" t="n">
-        <v>0.04307445696745881</v>
+        <v>0.04246505540611724</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05475311190399069</v>
+        <v>0.05274269692757804</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0891411758415829</v>
+        <v>0.08706536517756784</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1881676775852747</v>
+        <v>0.1853975587218747</v>
       </c>
     </row>
     <row r="16">
@@ -819,25 +819,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07455289909647499</v>
+        <v>0.07257332307277907</v>
       </c>
       <c r="C16" t="n">
-        <v>0.008677549097905558</v>
+        <v>0.008664507810538678</v>
       </c>
       <c r="D16" t="n">
-        <v>11.05878832989381</v>
+        <v>10.69332017482796</v>
       </c>
       <c r="E16" t="n">
-        <v>0.04017530756650255</v>
+        <v>0.04231528875390682</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05754097458746286</v>
+        <v>0.0555869811331425</v>
       </c>
       <c r="G16" t="n">
-        <v>0.09156482360548718</v>
+        <v>0.0895596650124157</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1907734328089629</v>
+        <v>0.1880668507420808</v>
       </c>
     </row>
     <row r="17">
@@ -847,25 +847,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.07528958210056472</v>
+        <v>0.07314333612773211</v>
       </c>
       <c r="C17" t="n">
-        <v>0.008640939338038599</v>
+        <v>0.008625480509481523</v>
       </c>
       <c r="D17" t="n">
-        <v>11.35585986782622</v>
+        <v>10.91736125042147</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0249703542156049</v>
+        <v>0.02472691637170212</v>
       </c>
       <c r="F17" t="n">
-        <v>0.05834907655275946</v>
+        <v>0.0562331600307807</v>
       </c>
       <c r="G17" t="n">
-        <v>0.09223008764836987</v>
+        <v>0.09005351222468344</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1915101158130526</v>
+        <v>0.1886368637970338</v>
       </c>
     </row>
     <row r="18">
@@ -875,22 +875,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1162205337124879</v>
+        <v>-0.1154935276693017</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01253467892277532</v>
+        <v>0.01254461589081859</v>
       </c>
       <c r="D18" t="n">
-        <v>-15.4380905202572</v>
+        <v>-15.50139222218442</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01882419988679694</v>
+        <v>0.01859640005833275</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1407934207662741</v>
+        <v>-0.1400858876151708</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.09164764665870184</v>
+        <v>-0.09090116772343276</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -903,25 +903,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.07828611377103283</v>
+        <v>0.07567437012770728</v>
       </c>
       <c r="C19" t="n">
-        <v>0.008575166622851921</v>
+        <v>0.008562763673645757</v>
       </c>
       <c r="D19" t="n">
-        <v>11.87429842691712</v>
+        <v>11.36895012819475</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02520922667591334</v>
+        <v>0.02505595269270936</v>
       </c>
       <c r="F19" t="n">
-        <v>0.06147606037796181</v>
+        <v>0.05888863068007112</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0950961671641038</v>
+        <v>0.09246010957534342</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1945066474835208</v>
+        <v>0.191167897797009</v>
       </c>
     </row>
     <row r="20">
@@ -931,25 +931,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08057695117083762</v>
+        <v>0.07772676058478324</v>
       </c>
       <c r="C20" t="n">
-        <v>0.009289761127057723</v>
+        <v>0.009273243616849582</v>
       </c>
       <c r="D20" t="n">
-        <v>11.92277877382736</v>
+        <v>11.38489904352828</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02815314867482911</v>
+        <v>0.02993630781480461</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06236609839545573</v>
+        <v>0.05954828823606638</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0987878039462195</v>
+        <v>0.09590523293350012</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1967974848833255</v>
+        <v>0.193220288254085</v>
       </c>
     </row>
     <row r="21">
@@ -959,25 +959,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.08427720798608049</v>
+        <v>0.08133026121231134</v>
       </c>
       <c r="C21" t="n">
-        <v>0.009337534876854294</v>
+        <v>0.009313585072042786</v>
       </c>
       <c r="D21" t="n">
-        <v>12.65246232189531</v>
+        <v>12.14062335126657</v>
       </c>
       <c r="E21" t="n">
-        <v>0.02681128183523957</v>
+        <v>0.0313811264480114</v>
       </c>
       <c r="F21" t="n">
-        <v>0.06597265414501301</v>
+        <v>0.06307265862381638</v>
       </c>
       <c r="G21" t="n">
-        <v>0.102581761827148</v>
+        <v>0.09958786380080636</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2004977416985684</v>
+        <v>0.1968237888816131</v>
       </c>
     </row>
     <row r="22">
@@ -987,25 +987,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.08303181943855802</v>
+        <v>0.07999630888156038</v>
       </c>
       <c r="C22" t="n">
-        <v>0.009025992529508232</v>
+        <v>0.009012943609906059</v>
       </c>
       <c r="D22" t="n">
-        <v>13.04893686287754</v>
+        <v>12.51502135600527</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03469757206667382</v>
+        <v>0.04030135404115386</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06533782118847553</v>
+        <v>0.06232789690807128</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1007258176886404</v>
+        <v>0.09766472085504944</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1992523531510459</v>
+        <v>0.1954898365508621</v>
       </c>
     </row>
     <row r="23">
@@ -1015,25 +1015,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.08828475537890729</v>
+        <v>0.08489037269654678</v>
       </c>
       <c r="C23" t="n">
-        <v>0.008705141796380966</v>
+        <v>0.008700874901246387</v>
       </c>
       <c r="D23" t="n">
-        <v>12.95078220764377</v>
+        <v>12.366389098831</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02260020994592784</v>
+        <v>0.024191647891674</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0712199074564837</v>
+        <v>0.06783389153468826</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1053496033013308</v>
+        <v>0.1019468538584052</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2045052890913952</v>
+        <v>0.2003839003658485</v>
       </c>
     </row>
     <row r="24">
@@ -1043,25 +1043,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.09012218200051153</v>
+        <v>0.08666802637170301</v>
       </c>
       <c r="C24" t="n">
-        <v>0.009152598291821379</v>
+        <v>0.009134733323126254</v>
       </c>
       <c r="D24" t="n">
-        <v>12.88489703750272</v>
+        <v>12.36846911708075</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03248491425092325</v>
+        <v>0.03207256154965631</v>
       </c>
       <c r="F24" t="n">
-        <v>0.07218006881263604</v>
+        <v>0.06876093745127225</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1080642951883869</v>
+        <v>0.1045751152921337</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2063427157129994</v>
+        <v>0.2021615540410047</v>
       </c>
     </row>
     <row r="25">
@@ -1071,25 +1071,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.09920758254248599</v>
+        <v>0.09596388473756264</v>
       </c>
       <c r="C25" t="n">
-        <v>0.009175826646502223</v>
+        <v>0.009091373778732301</v>
       </c>
       <c r="D25" t="n">
-        <v>14.26386389952369</v>
+        <v>13.85785758488528</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01469418477787258</v>
+        <v>0.02432308989728413</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08122010587443278</v>
+        <v>0.07814197181300717</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1171950592105392</v>
+        <v>0.113785797662118</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2154281162549739</v>
+        <v>0.2114574124068644</v>
       </c>
     </row>
     <row r="26">
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1024377258300269</v>
+        <v>0.09984132992821479</v>
       </c>
       <c r="C26" t="n">
-        <v>0.009207981224574481</v>
+        <v>0.009148882153142301</v>
       </c>
       <c r="D26" t="n">
-        <v>14.57300151360771</v>
+        <v>14.17166567111888</v>
       </c>
       <c r="E26" t="n">
-        <v>0.01366177734269737</v>
+        <v>0.01377446349096568</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08438714453380632</v>
+        <v>0.08190661166020104</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1204883071262474</v>
+        <v>0.1177760481962284</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2186582595425148</v>
+        <v>0.2153348575975165</v>
       </c>
     </row>
     <row r="27">
@@ -1127,25 +1127,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1038443713201875</v>
+        <v>0.1009704587895336</v>
       </c>
       <c r="C27" t="n">
-        <v>0.009298227873855947</v>
+        <v>0.009240322179030773</v>
       </c>
       <c r="D27" t="n">
-        <v>14.37158067603893</v>
+        <v>13.90136062959721</v>
       </c>
       <c r="E27" t="n">
-        <v>0.03270904977906969</v>
+        <v>0.03814052233962318</v>
       </c>
       <c r="F27" t="n">
-        <v>0.08561703457399401</v>
+        <v>0.08285664449957485</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1220717080663811</v>
+        <v>0.1190842730794925</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2200649050326755</v>
+        <v>0.2164639864588354</v>
       </c>
     </row>
     <row r="28">
@@ -1155,25 +1155,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1045973719965627</v>
+        <v>0.1020053434561296</v>
       </c>
       <c r="C28" t="n">
-        <v>0.009541683941681636</v>
+        <v>0.009619316928696067</v>
       </c>
       <c r="D28" t="n">
-        <v>14.24236688609829</v>
+        <v>13.77088194503329</v>
       </c>
       <c r="E28" t="n">
-        <v>0.04827849949460525</v>
+        <v>0.05311058001682764</v>
       </c>
       <c r="F28" t="n">
-        <v>0.08589279732843817</v>
+        <v>0.08314860291536971</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1233019466646873</v>
+        <v>0.1208620839968896</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2208179057090506</v>
+        <v>0.2174988711254313</v>
       </c>
     </row>
     <row r="29">
@@ -1183,25 +1183,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.08277799444486302</v>
+        <v>0.08275824942599032</v>
       </c>
       <c r="C29" t="n">
-        <v>0.004224814433532974</v>
+        <v>0.004223224178787807</v>
       </c>
       <c r="D29" t="n">
-        <v>6.650108748883514</v>
+        <v>6.649215006051794</v>
       </c>
       <c r="E29" t="n">
-        <v>6.268562128291161e-47</v>
+        <v>6.172858889691291e-47</v>
       </c>
       <c r="F29" t="n">
-        <v>0.07449632753429432</v>
+        <v>0.07447969990228524</v>
       </c>
       <c r="G29" t="n">
-        <v>0.09105966135543204</v>
+        <v>0.09103679894969537</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1989985281573509</v>
+        <v>0.1982517770952921</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year-4final.xlsx
+++ b/hourly datasets/cap_gen_year-4final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2446944638728799</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1154935276693017</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1171162419126958</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1151689754377776</v>
+        <v>0.3179697989918662</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2306625031070793</v>
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1903915770316821</v>
       </c>
     </row>
     <row r="4">
@@ -513,25 +524,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1320184843607762</v>
+        <v>0.2915500913161409</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01170019730839802</v>
+        <v>0.0109297855303166</v>
       </c>
       <c r="D4" t="n">
-        <v>20.33795207942311</v>
+        <v>16.9157496839741</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02942285767024194</v>
+        <v>0.02904614483371622</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1090819976461664</v>
+        <v>0.0933060324037996</v>
       </c>
       <c r="G4" t="n">
-        <v>0.154954971075386</v>
+        <v>0.1361585585957575</v>
       </c>
       <c r="H4" t="n">
-        <v>0.247512012030078</v>
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1639718693559568</v>
       </c>
     </row>
     <row r="5">
@@ -541,25 +555,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1229358397398398</v>
+        <v>0.3429164079648739</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008153486261766405</v>
+        <v>0.008209717201502726</v>
       </c>
       <c r="D5" t="n">
-        <v>20.49766085983692</v>
+        <v>20.63902403818062</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02872852238743644</v>
+        <v>0.02892665012803945</v>
       </c>
       <c r="F5" t="n">
-        <v>0.106953036402549</v>
+        <v>0.1076906435501528</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1389186430771301</v>
+        <v>0.1398767026845587</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2384293674091415</v>
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2153381860046899</v>
       </c>
     </row>
     <row r="6">
@@ -569,25 +586,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08784781135881332</v>
+        <v>0.3287872541041822</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008400432006278878</v>
+        <v>0.01901672421692532</v>
       </c>
       <c r="D6" t="n">
-        <v>5.302672238745703</v>
+        <v>13.483725599328</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004269925483494016</v>
+        <v>0.004588254913542671</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07138091588087987</v>
+        <v>0.1933805815553416</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1043147068367472</v>
+        <v>0.2679353847000371</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2033413390281151</v>
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2012090321439982</v>
       </c>
     </row>
     <row r="7">
@@ -597,25 +617,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1007733505490333</v>
+        <v>0.3715206539768175</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008339427380790658</v>
+        <v>0.01982690241378665</v>
       </c>
       <c r="D7" t="n">
-        <v>5.518479211794017</v>
+        <v>15.93704754988779</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002769676848125113</v>
+        <v>0.0003294024178526217</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08442604931908698</v>
+        <v>0.2449855164710783</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1171206517789791</v>
+        <v>0.3227165869042381</v>
       </c>
       <c r="H7" t="n">
-        <v>0.216266878218335</v>
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2439424320166335</v>
       </c>
     </row>
     <row r="8">
@@ -625,25 +648,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08075139283429086</v>
+        <v>0.3193384572326816</v>
       </c>
       <c r="C8" t="n">
-        <v>0.005159491644942366</v>
+        <v>0.01531817557222983</v>
       </c>
       <c r="D8" t="n">
-        <v>5.299644615466241</v>
+        <v>15.80828374647695</v>
       </c>
       <c r="E8" t="n">
-        <v>2.174010277790305e-41</v>
+        <v>2.258387177497964e-41</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0706375321450093</v>
+        <v>0.2103734536567366</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09086525352357294</v>
+        <v>0.2704281406802818</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1962449205035926</v>
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1917602352724976</v>
       </c>
     </row>
     <row r="9">
@@ -653,25 +679,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08389329607192834</v>
+        <v>0.3286437895558219</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004714228005401442</v>
+        <v>0.01396869523992781</v>
       </c>
       <c r="D9" t="n">
-        <v>6.031779678291385</v>
+        <v>18.01274718807795</v>
       </c>
       <c r="E9" t="n">
-        <v>4.984856753996613e-44</v>
+        <v>5.178327209350803e-44</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07465225991802206</v>
+        <v>0.222324094375539</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09313433222583486</v>
+        <v>0.2770881646077601</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1993868237412301</v>
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.2010655675956378</v>
       </c>
     </row>
     <row r="10">
@@ -681,25 +710,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07956891151227333</v>
+        <v>0.3155352944702979</v>
       </c>
       <c r="C10" t="n">
-        <v>0.004284433690004747</v>
+        <v>0.01267258965439247</v>
       </c>
       <c r="D10" t="n">
-        <v>6.299803315822223</v>
+        <v>18.8180876078648</v>
       </c>
       <c r="E10" t="n">
-        <v>1.133846806388912e-45</v>
+        <v>1.177853258080445e-45</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07117037643419094</v>
+        <v>0.2117562804173901</v>
       </c>
       <c r="G10" t="n">
-        <v>0.08796744659035587</v>
+        <v>0.2614389883948609</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1950624391815751</v>
+        <v>6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1879570725101138</v>
       </c>
     </row>
     <row r="11">
@@ -709,7 +741,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03818192031798831</v>
+        <v>0.2861617054590648</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -717,7 +749,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.15367544798729</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1585834834988807</v>
       </c>
     </row>
     <row r="12">
@@ -727,7 +762,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05112482702232342</v>
+        <v>0.3027123616367527</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -735,7 +770,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1666183546916252</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1751341396765686</v>
       </c>
     </row>
     <row r="13">
@@ -745,25 +783,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05730233015657719</v>
+        <v>0.3119528493677421</v>
       </c>
       <c r="C13" t="n">
-        <v>0.008944364535980229</v>
+        <v>0.008937338104557015</v>
       </c>
       <c r="D13" t="n">
-        <v>7.787680738114978</v>
+        <v>7.781127452248292</v>
       </c>
       <c r="E13" t="n">
-        <v>0.04035651114324693</v>
+        <v>0.04033626845095219</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03976774481781017</v>
+        <v>0.03973229001797033</v>
       </c>
       <c r="G13" t="n">
-        <v>0.07483691549534413</v>
+        <v>0.07477391263458961</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1727958578258789</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.184374627407558</v>
       </c>
     </row>
     <row r="14">
@@ -773,7 +814,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06315694696446089</v>
+        <v>0.317495714201756</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -781,7 +822,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1786504746337626</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1899174922415719</v>
       </c>
     </row>
     <row r="15">
@@ -791,25 +835,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06990403105257292</v>
+        <v>0.3228360886967814</v>
       </c>
       <c r="C15" t="n">
-        <v>0.008753978502926555</v>
+        <v>0.008737857992784901</v>
       </c>
       <c r="D15" t="n">
-        <v>10.17803388647727</v>
+        <v>10.1584745666535</v>
       </c>
       <c r="E15" t="n">
-        <v>0.04246505540611724</v>
+        <v>0.04243503531040909</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05274269692757804</v>
+        <v>0.0526276356321735</v>
       </c>
       <c r="G15" t="n">
-        <v>0.08706536517756784</v>
+        <v>0.08688710175912023</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1853975587218747</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1952578667365974</v>
       </c>
     </row>
     <row r="16">
@@ -819,25 +866,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07257332307277907</v>
+        <v>0.3252845350267428</v>
       </c>
       <c r="C16" t="n">
-        <v>0.008664507810538678</v>
+        <v>0.008640487010558071</v>
       </c>
       <c r="D16" t="n">
-        <v>10.69332017482796</v>
+        <v>10.66187019800597</v>
       </c>
       <c r="E16" t="n">
-        <v>0.04231528875390682</v>
+        <v>0.04229117830927036</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0555869811331425</v>
+        <v>0.05540487661038994</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0895596650124157</v>
+        <v>0.08928338428045164</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1880668507420808</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1977063130665588</v>
       </c>
     </row>
     <row r="17">
@@ -847,25 +897,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.07314333612773211</v>
+        <v>0.3259006427158213</v>
       </c>
       <c r="C17" t="n">
-        <v>0.008625480509481523</v>
+        <v>0.008605221901966635</v>
       </c>
       <c r="D17" t="n">
-        <v>10.91736125042147</v>
+        <v>10.89049329869334</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02472691637170212</v>
+        <v>0.02470220241457424</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0562331600307807</v>
+        <v>0.05608101607019103</v>
       </c>
       <c r="G17" t="n">
-        <v>0.09005351222468344</v>
+        <v>0.08982193936090567</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1886368637970338</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1983224207556372</v>
       </c>
     </row>
     <row r="18">
@@ -875,24 +928,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1154935276693017</v>
+        <v>0.1275782219601841</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01254461589081859</v>
+        <v>0.01248593632388465</v>
       </c>
       <c r="D18" t="n">
-        <v>-15.50139222218442</v>
+        <v>-15.42362017708355</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01859640005833275</v>
+        <v>0.01854196971400626</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1400858876151708</v>
+        <v>-0.1394276344846299</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.09090116772343276</v>
+        <v>-0.0904729748972381</v>
       </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -903,25 +959,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.07567437012770728</v>
+        <v>0.3290786474885763</v>
       </c>
       <c r="C19" t="n">
-        <v>0.008562763673645757</v>
+        <v>0.008533618851674302</v>
       </c>
       <c r="D19" t="n">
-        <v>11.36895012819475</v>
+        <v>11.3284961045021</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02505595269270936</v>
+        <v>0.02500402750028025</v>
       </c>
       <c r="F19" t="n">
-        <v>0.05888863068007112</v>
+        <v>0.05865750732169143</v>
       </c>
       <c r="G19" t="n">
-        <v>0.09246010957534342</v>
+        <v>0.09211472211897843</v>
       </c>
       <c r="H19" t="n">
-        <v>0.191167897797009</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2015004255283923</v>
       </c>
     </row>
     <row r="20">
@@ -931,25 +990,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.07772676058478324</v>
+        <v>0.3299146687852249</v>
       </c>
       <c r="C20" t="n">
-        <v>0.009273243616849582</v>
+        <v>0.009234783875042505</v>
       </c>
       <c r="D20" t="n">
-        <v>11.38489904352828</v>
+        <v>11.3381227765673</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02993630781480461</v>
+        <v>0.02987774488706133</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05954828823606638</v>
+        <v>0.05926291023975194</v>
       </c>
       <c r="G20" t="n">
-        <v>0.09590523293350012</v>
+        <v>0.09546906918057352</v>
       </c>
       <c r="H20" t="n">
-        <v>0.193220288254085</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2023364468250408</v>
       </c>
     </row>
     <row r="21">
@@ -959,25 +1021,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.08133026121231134</v>
+        <v>0.3300662278897786</v>
       </c>
       <c r="C21" t="n">
-        <v>0.009313585072042786</v>
+        <v>0.009248110648912185</v>
       </c>
       <c r="D21" t="n">
-        <v>12.14062335126657</v>
+        <v>12.06311683871631</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0313811264480114</v>
+        <v>0.03128970482965437</v>
       </c>
       <c r="F21" t="n">
-        <v>0.06307265862381638</v>
+        <v>0.06256632660947731</v>
       </c>
       <c r="G21" t="n">
-        <v>0.09958786380080636</v>
+        <v>0.09882482995241787</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1968237888816131</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2024880059295945</v>
       </c>
     </row>
     <row r="22">
@@ -987,25 +1052,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.07999630888156038</v>
+        <v>0.3252929965811113</v>
       </c>
       <c r="C22" t="n">
-        <v>0.009012943609906059</v>
+        <v>0.008925692066903218</v>
       </c>
       <c r="D22" t="n">
-        <v>12.51502135600527</v>
+        <v>12.38487733469616</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04030135404115386</v>
+        <v>0.04008300191187036</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06232789690807128</v>
+        <v>0.06165187231592521</v>
       </c>
       <c r="G22" t="n">
-        <v>0.09766472085504944</v>
+        <v>0.0966466029335829</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1954898365508621</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1977147746209272</v>
       </c>
     </row>
     <row r="23">
@@ -1015,25 +1083,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.08489037269654678</v>
+        <v>0.3261337513181191</v>
       </c>
       <c r="C23" t="n">
-        <v>0.008700874901246387</v>
+        <v>0.008594836537324509</v>
       </c>
       <c r="D23" t="n">
-        <v>12.366389098831</v>
+        <v>12.04717159390203</v>
       </c>
       <c r="E23" t="n">
-        <v>0.024191647891674</v>
+        <v>0.02410203858946839</v>
       </c>
       <c r="F23" t="n">
-        <v>0.06783389153468826</v>
+        <v>0.06623578916308386</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1019468538584052</v>
+        <v>0.09993302368135557</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2003839003658485</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.198555529357935</v>
       </c>
     </row>
     <row r="24">
@@ -1043,25 +1114,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.08666802637170301</v>
+        <v>0.3255475458727413</v>
       </c>
       <c r="C24" t="n">
-        <v>0.009134733323126254</v>
+        <v>0.009005770450693612</v>
       </c>
       <c r="D24" t="n">
-        <v>12.36846911708075</v>
+        <v>12.00942098206804</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03207256154965631</v>
+        <v>0.03172328799061182</v>
       </c>
       <c r="F24" t="n">
-        <v>0.06876093745127225</v>
+        <v>0.06695247877594757</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1045751152921337</v>
+        <v>0.1022610517073555</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2021615540410047</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1979693239125572</v>
       </c>
     </row>
     <row r="25">
@@ -1071,25 +1145,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.09596388473756264</v>
+        <v>0.3260855209567263</v>
       </c>
       <c r="C25" t="n">
-        <v>0.009091373778732301</v>
+        <v>0.008888544511880071</v>
       </c>
       <c r="D25" t="n">
-        <v>13.85785758488528</v>
+        <v>12.98747200339553</v>
       </c>
       <c r="E25" t="n">
-        <v>0.02432308989728413</v>
+        <v>0.02424325051937537</v>
       </c>
       <c r="F25" t="n">
-        <v>0.07814197181300717</v>
+        <v>0.0740177089624264</v>
       </c>
       <c r="G25" t="n">
-        <v>0.113785797662118</v>
+        <v>0.1088663356738983</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2114574124068644</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.1985072989965422</v>
       </c>
     </row>
     <row r="26">
@@ -1099,25 +1176,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.09984132992821479</v>
+        <v>0.327678763896358</v>
       </c>
       <c r="C26" t="n">
-        <v>0.009148882153142301</v>
+        <v>0.008923609371398638</v>
       </c>
       <c r="D26" t="n">
-        <v>14.17166567111888</v>
+        <v>13.19477130437106</v>
       </c>
       <c r="E26" t="n">
-        <v>0.01377446349096568</v>
+        <v>0.01369874889865633</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08190661166020104</v>
+        <v>0.07728391932051176</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1177760481962284</v>
+        <v>0.1122701664335282</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2153348575975165</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2001005419361739</v>
       </c>
     </row>
     <row r="27">
@@ -1127,25 +1207,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1009704587895336</v>
+        <v>0.3261577166574556</v>
       </c>
       <c r="C27" t="n">
-        <v>0.009240322179030773</v>
+        <v>0.008990481992075441</v>
       </c>
       <c r="D27" t="n">
-        <v>13.90136062959721</v>
+        <v>12.8235546229285</v>
       </c>
       <c r="E27" t="n">
-        <v>0.03814052233962318</v>
+        <v>0.03779266357727897</v>
       </c>
       <c r="F27" t="n">
-        <v>0.08285664449957485</v>
+        <v>0.07774905749034007</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1190842730794925</v>
+        <v>0.1129971792596776</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2164639864588354</v>
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1985794946972715</v>
       </c>
     </row>
     <row r="28">
@@ -1155,25 +1238,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1020053434561296</v>
+        <v>0.3266645889845783</v>
       </c>
       <c r="C28" t="n">
-        <v>0.009619316928696067</v>
+        <v>0.009358246803074559</v>
       </c>
       <c r="D28" t="n">
-        <v>13.77088194503329</v>
+        <v>12.63864656271602</v>
       </c>
       <c r="E28" t="n">
-        <v>0.05311058001682764</v>
+        <v>0.05255964932447185</v>
       </c>
       <c r="F28" t="n">
-        <v>0.08314860291536971</v>
+        <v>0.07778912029888373</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1208620839968896</v>
+        <v>0.1144790671070934</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2174988711254313</v>
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.1990863670243942</v>
       </c>
     </row>
     <row r="29">
@@ -1183,25 +1269,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.08275824942599032</v>
+        <v>0.3251561221125097</v>
       </c>
       <c r="C29" t="n">
-        <v>0.004223224178787807</v>
+        <v>0.01249083170478929</v>
       </c>
       <c r="D29" t="n">
-        <v>6.649215006051794</v>
+        <v>19.87029525481471</v>
       </c>
       <c r="E29" t="n">
-        <v>6.172858889691291e-47</v>
+        <v>6.412437653768773e-47</v>
       </c>
       <c r="F29" t="n">
-        <v>0.07447969990228524</v>
+        <v>0.2217333977724662</v>
       </c>
       <c r="G29" t="n">
-        <v>0.09103679894969537</v>
+        <v>0.2707035263242079</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1982517770952921</v>
+        <v>6</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1975779001523256</v>
       </c>
     </row>
   </sheetData>
